--- a/class1/excel/exponential_model.xlsx
+++ b/class1/excel/exponential_model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\snguyen4\Dropbox\git\math110\class1\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{373C5067-B0DE-464B-B72F-D54F59AEFEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1C06B7-8B0E-4B77-AFC2-5013482A9D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{B5681A13-B006-49E5-BF8C-5B165EEA9532}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" activeTab="1" xr2:uid="{B5681A13-B006-49E5-BF8C-5B165EEA9532}"/>
   </bookViews>
   <sheets>
     <sheet name="Example" sheetId="1" r:id="rId1"/>
@@ -188,10 +188,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -206,32 +206,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -310,6 +284,32 @@
           <color theme="4" tint="0.39997558519241921"/>
         </left>
       </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1722,6 +1722,401 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="exp"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="exp"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="exp"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Assignment 11'!$M$6:$M$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Assignment 11'!$N$6:$N$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>52.68</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>54.06</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>56.19</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>58.41</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>61.36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>61.52</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A98F-44E7-9055-EAF4F6A0DC45}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1875107519"/>
+        <c:axId val="1875099359"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1875107519"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1875099359"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1875099359"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1875107519"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1842,6 +2237,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -2875,6 +3310,522 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3557,8 +4508,8 @@
       <xdr:row>68</xdr:row>
       <xdr:rowOff>10734</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="18" name="Ink 17">
@@ -3577,7 +4528,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="18" name="Ink 17">
@@ -3622,8 +4573,8 @@
       <xdr:row>67</xdr:row>
       <xdr:rowOff>144554</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="19" name="Ink 18">
@@ -3642,7 +4593,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="19" name="Ink 18">
@@ -3687,8 +4638,8 @@
       <xdr:row>67</xdr:row>
       <xdr:rowOff>156794</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="29" name="Ink 28">
@@ -3707,7 +4658,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="29" name="Ink 28">
@@ -3752,8 +4703,8 @@
       <xdr:row>66</xdr:row>
       <xdr:rowOff>163351</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="30" name="Ink 29">
@@ -3772,7 +4723,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="30" name="Ink 29">
@@ -3817,8 +4768,8 @@
       <xdr:row>66</xdr:row>
       <xdr:rowOff>163351</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="34" name="Ink 33">
@@ -3837,7 +4788,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="34" name="Ink 33">
@@ -3882,8 +4833,8 @@
       <xdr:row>66</xdr:row>
       <xdr:rowOff>176671</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="37" name="Ink 36">
@@ -3902,7 +4853,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="37" name="Ink 36">
@@ -3947,8 +4898,8 @@
       <xdr:row>67</xdr:row>
       <xdr:rowOff>152292</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="42" name="Ink 41">
@@ -3967,7 +4918,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="42" name="Ink 41">
@@ -4048,6 +4999,42 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>320040</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAF8C0D6-B294-95C7-4DD3-238CFC559BC5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4080,8 +5067,8 @@
     </inkml:brush>
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">45 116 704 0 0,'-2'-1'683'0'0,"0"1"0"0"0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-3-3 0 0 0,3 4-591 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,0-1-1 0 0,4-2 193 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,12-6 1 0 0,-16 9-267 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 1 1 0 0,0-1-1 0 0,3 2 0 0 0,-3-1-13 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 4-1 0 0,-13 53-100 0 0,-62 167 309 0 0,75-225-127 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1-1 0 0,1 4 1 0 0,-1-5-40 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,2 0-124 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,2-2 0 0 0,1-1-997 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,13-6 1 0 0,-13 8 416 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="276.96">295 401 9370 0 0,'2'3'448'0'0,"-2"-2"-480"0"0,0 0-376 0 0,0-2 400 0 0,1-1 448 0 0,-1-1-416 0 0,1-3-296 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1174.68">442 90 3089 0 0,'0'0'108'0'0,"-1"0"0"0"0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,15-16 3374 0 0,26-12-451 0 0,-38 27-2862 0 0,30-13 470 0 0,-31 14-625 0 0,-1 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,3 2 0 0 0,-4-1-9 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 1 1 0 0,0 1-1 0 0,-12 30-55 0 0,10-29 39 0 0,-6 16-306 0 0,-14 33-918 0 0,22-51 1200 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,2 0 0 0 0,0 2-1 0 0,0-2 31 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,3 0 0 0 0,19 13 68 0 0,-22-12-44 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,0-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,-4 4 1 0 0,3-2 64 0 0,0-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0-1 0 0 0,-10 7 0 0 0,14-9-193 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-3 0-1 0 0,4 0-145 0 0,0 0-1 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,0-2-1 0 0,0-6-4058 0 0,1 5 992 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="276.95">295 401 9370 0 0,'2'3'448'0'0,"-2"-2"-480"0"0,0 0-376 0 0,0-2 400 0 0,1-1 448 0 0,-1-1-416 0 0,1-3-296 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1174.67">442 90 3089 0 0,'0'0'108'0'0,"-1"0"0"0"0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,15-16 3374 0 0,26-12-451 0 0,-38 27-2862 0 0,30-13 470 0 0,-31 14-625 0 0,-1 0 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,3 2 0 0 0,-4-1-9 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 1 1 0 0,0 1-1 0 0,-12 30-55 0 0,10-29 39 0 0,-6 16-306 0 0,-14 33-918 0 0,22-51 1200 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,2 0 0 0 0,0 2-1 0 0,0-2 31 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,3 0 0 0 0,19 13 68 0 0,-22-12-44 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,0-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,0-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,-4 4 1 0 0,3-2 64 0 0,0-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0-1 0 0 0,-10 7 0 0 0,14-9-193 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,-3 0-1 0 0,4 0-145 0 0,0 0-1 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,0-2-1 0 0,0-6-4058 0 0,1 5 992 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1763.31">813 88 4873 0 0,'-1'-1'357'0'0,"-1"0"0"0"0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,-2 1 0 0 0,1 0-127 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-3 6 0 0 0,-3 5-283 0 0,2 0 0 0 0,0 1 1 0 0,0 0-1 0 0,-2 17 0 0 0,5-24 27 0 0,-9 53-18 0 0,11-57 30 0 0,1 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,2 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,3 6 0 0 0,-3-8 7 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,2-3 0 0 0,4-1 5 0 0,0 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,8-9 0 0 0,-11 10 79 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,4-12 1 0 0,-7 16 15 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,-3-4-1 0 0,-5-3 603 0 0,-11-10-3374 0 0,21 18 2535 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,1-1 1 0 0,2-3-1262 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2276.8">943 100 5353 0 0,'-4'12'5300'0'0,"-9"10"-3030"0"0,-1 0-1627 0 0,3 3-437 0 0,-9 36 0 0 0,17-54-221 0 0,2 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 1-1 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,3 11-1 0 0,-3-18 9 0 0,1 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,1 0 0 0 0,22-5-107 0 0,-19 2 104 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,-1-1 0 0 0,1 0 0 0 0,4-4 1 0 0,11-13-377 0 0,-13 14 813 0 0,0 0-1 0 0,-1-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,8-15 0 0 0,-13 21-289 0 0,0-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,-2-2 1 0 0,-20-13 319 0 0,5 4-1557 0 0,10 3-4171 0 0,11 4 1106 0 0,1 2-546 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2815.63">1144 103 5097 0 0,'1'-1'696'0'0,"0"-1"-1"0"0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,3-1-1 0 0,20-9 2659 0 0,-24 11-3327 0 0,1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 2 0 0 0,0 13-47 0 0,0 0-1 0 0,-2 0 0 0 0,0 0 1 0 0,-7 22-1 0 0,6-25-15 0 0,0 0 0 0 0,1-1 0 0 0,0 2 0 0 0,1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,1 19 0 0 0,0-31 40 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 0 0 0 0,32-31-1910 0 0,-26 25-767 0 0,-1 2 1277 0 0,0 2-603 0 0</inkml:trace>
@@ -4285,33 +5272,33 @@
     </inkml:brush>
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">56 26 7106 0 0,'-3'6'-777'0'0,"1"-1"1201"0"0,0-2 97 0 0,1 2-217 0 0,-1-1-56 0 0,1 0-336 0 0,0 0-32 0 0,0-1-168 0 0,0 1 184 0 0,1 1-2313 0 0,-1-1 3833 0 0,-1-1-1784 0 0,2 1 320 0 0,-1 2-696 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="557.93">24 28 5137 0 0,'1'3'1640'0'0,"0"-1"-1800"0"0,5 4 6506 0 0,-4-2-5714 0 0,1-1-232 0 0,1 2 376 0 0,-1-1-952 0 0,1 0 128 0 0,0-1 40 0 0,-1 0 24 0 0,1 0-768 0 0,4-1-7482 0 0,-2-3 4705 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="557.92">24 28 5137 0 0,'1'3'1640'0'0,"0"-1"-1800"0"0,5 4 6506 0 0,-4-2-5714 0 0,1-1-232 0 0,1 2 376 0 0,-1-1-952 0 0,1 0 128 0 0,0-1 40 0 0,-1 0 24 0 0,1 0-768 0 0,4-1-7482 0 0,-2-3 4705 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="822.75">3 72 8930 0 0,'-3'5'192'0'0,"5"-5"1472"0"0,1 0-647 0 0,2 0 639 0 0,2-1-2072 0 0,0-3 504 0 0,1 0-152 0 0,0-1 184 0 0,1 1-1104 0 0,-1-2-1161 0 0,-4 1-847 0 0,2 0 1191 0 0,4-2-647 0 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1161.9">55 1 8346 0 0,'-5'5'1992'0'0,"4"-3"-1832"0"0,-2 3 744 0 0,3-1 977 0 0,-1 2-2265 0 0,-1-1 624 0 0,2 1-208 0 0,2 0 8 0 0,-2-1-736 0 0,-1 0-1705 0 0,3-1 3713 0 0,0 1-1320 0 0,-1-2-384 0 0,2-2-296 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{19BAAB04-9B4E-4D87-B466-F528EDDFBD38}" name="Table1" displayName="Table1" ref="A10:B15" totalsRowShown="0" headerRowDxfId="13" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{19BAAB04-9B4E-4D87-B466-F528EDDFBD38}" name="Table1" displayName="Table1" ref="A10:B15" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="A10:B15" xr:uid="{19BAAB04-9B4E-4D87-B466-F528EDDFBD38}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3F88F5B5-F293-4646-B6C8-5F94909CA54C}" name="Year " dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{8C5A681B-39D0-4C70-9EAF-BC5297705DC6}" name="Population" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{3F88F5B5-F293-4646-B6C8-5F94909CA54C}" name="Year " dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{8C5A681B-39D0-4C70-9EAF-BC5297705DC6}" name="Population" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B92CCABF-0BC4-4A2E-B364-9480640F27F8}" name="Table13" displayName="Table13" ref="A34:D39" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B92CCABF-0BC4-4A2E-B364-9480640F27F8}" name="Table13" displayName="Table13" ref="A34:D39" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="A34:D39" xr:uid="{B92CCABF-0BC4-4A2E-B364-9480640F27F8}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{EF430202-7EBC-43F7-AAF5-F2FBE147DAF1}" name="Year (Since 2012)" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{B9CD2F5E-20BD-4060-8C36-2D575D337D75}" name="Population" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{5590AA15-FE87-48DF-B443-CA7F24529ACA}" name="Esitmated Pop" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{EF430202-7EBC-43F7-AAF5-F2FBE147DAF1}" name="Year (Since 2012)" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{B9CD2F5E-20BD-4060-8C36-2D575D337D75}" name="Population" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{5590AA15-FE87-48DF-B443-CA7F24529ACA}" name="Esitmated Pop" dataDxfId="8">
       <calculatedColumnFormula>2.3002*EXP(1)^(0.0863*Table13[[#This Row],[Year (Since 2012)]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{AC6B3A4D-C02A-4D50-B945-825F1054E321}" name="Absolute Error Percentage" dataDxfId="0">
+    <tableColumn id="4" xr3:uid="{AC6B3A4D-C02A-4D50-B945-825F1054E321}" name="Absolute Error Percentage" dataDxfId="7">
       <calculatedColumnFormula xml:space="preserve"> ABS((Table13[[#This Row],[Population]]-Table13[[#This Row],[Esitmated Pop]])/Table13[[#This Row],[Population]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4320,15 +5307,15 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B47CF780-F992-421C-A72C-DDF73AEB83DF}" name="Table3" displayName="Table3" ref="A48:D53" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B47CF780-F992-421C-A72C-DDF73AEB83DF}" name="Table3" displayName="Table3" ref="A48:D53" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5" tableBorderDxfId="4">
   <autoFilter ref="A48:D53" xr:uid="{B47CF780-F992-421C-A72C-DDF73AEB83DF}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{7EEF1895-823A-41E4-9DB2-8BAD075D5A3F}" name="Year (Since 2012)" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{993A7418-9F1B-4E02-85C0-35B16F032E82}" name="Population" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{5F4DF801-3524-45DE-904F-F2C709FE9D10}" name="Estimated Pop" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{7EEF1895-823A-41E4-9DB2-8BAD075D5A3F}" name="Year (Since 2012)" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{993A7418-9F1B-4E02-85C0-35B16F032E82}" name="Population" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{5F4DF801-3524-45DE-904F-F2C709FE9D10}" name="Estimated Pop" dataDxfId="1">
       <calculatedColumnFormula>0.237*A49+2.28</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{789EA415-E1F0-4185-A3FB-43B40A149BB6}" name="Absolute Error Percentage" dataDxfId="7">
+    <tableColumn id="4" xr3:uid="{789EA415-E1F0-4185-A3FB-43B40A149BB6}" name="Absolute Error Percentage" dataDxfId="0">
       <calculatedColumnFormula>ABS((Table3[[#This Row],[Population]]-Table3[[#This Row],[Estimated Pop]])/Table3[[#This Row],[Population]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4985,12 +5972,60 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204FE8B1-6611-484E-AAF5-F08D8BE8C592}">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>52.68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>54.06</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M8">
+        <v>2</v>
+      </c>
+      <c r="N8">
+        <v>56.19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M9">
+        <v>3</v>
+      </c>
+      <c r="N9">
+        <v>58.41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M10">
+        <v>4</v>
+      </c>
+      <c r="N10">
+        <v>61.36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M11">
+        <v>5</v>
+      </c>
+      <c r="N11">
+        <v>61.52</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
